--- a/output/laminas_provinciales/prov_i_peringrmin_a_2023_aysen.xlsx
+++ b/output/laminas_provinciales/prov_i_peringrmin_a_2023_aysen.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 11:18</t>
+    <t xml:space="preserve">2026-09-09 22:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/laminas_provinciales/prov_i_peringrmin_a_2023_aysen.xlsx
+++ b/output/laminas_provinciales/prov_i_peringrmin_a_2023_aysen.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:18</t>
+    <t xml:space="preserve">2026-09-17 13:44</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -955,26 +955,26 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>2.49</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>2.72</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>2.97</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="5">
@@ -1015,101 +1015,101 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>3.57</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>2.49</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>3.11</v>
+        <v>3.71</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>4.04</v>
+        <v>3.57</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>2.72</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>4.51</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>4.07</v>
+        <v>4.04</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>2.97</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>3.71</v>
+        <v>4.51</v>
       </c>
     </row>
     <row r="11">

--- a/output/laminas_provinciales/prov_i_peringrmin_a_2023_aysen.xlsx
+++ b/output/laminas_provinciales/prov_i_peringrmin_a_2023_aysen.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:44</t>
+    <t xml:space="preserve">2026-09-25 21:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -527,10 +527,10 @@
         <v>4.63</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>-1.33</v>
+        <v>-1.32</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-28.73</v>
+        <v>-28.62</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>5</v>
@@ -576,7 +576,7 @@
         <v>-1.08</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-30.25</v>
+        <v>-30.28</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>5</v>
@@ -599,7 +599,7 @@
         <v>-1.06</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-26.3</v>
+        <v>-26.24</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>4</v>
@@ -622,7 +622,7 @@
         <v>-1.58</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-39.01</v>
+        <v>-39.03</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>4</v>
@@ -645,7 +645,7 @@
         <v>-1.32</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-32.67</v>
+        <v>-32.59</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>4</v>
@@ -668,7 +668,7 @@
         <v>-1.24</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-26.55</v>
+        <v>-26.49</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>3</v>
@@ -691,7 +691,7 @@
         <v>-0.96</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-29</v>
+        <v>-29.01</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>3</v>
@@ -714,7 +714,7 @@
         <v>-1.09</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-27.53</v>
+        <v>-27.47</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>3</v>
@@ -737,7 +737,7 @@
         <v>-1.23</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-26.39</v>
+        <v>-26.37</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>2</v>
@@ -760,7 +760,7 @@
         <v>-0.99</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-28.45</v>
+        <v>-28.47</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>2</v>
@@ -783,7 +783,7 @@
         <v>-1.1</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-27.03</v>
+        <v>-27.11</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>2</v>
@@ -806,7 +806,7 @@
         <v>-1.04</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-19.08</v>
+        <v>-19.02</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>1</v>
@@ -829,7 +829,7 @@
         <v>-0.63</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-14.89</v>
+        <v>-14.97</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>1</v>
@@ -852,7 +852,7 @@
         <v>-0.8</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-16.81</v>
+        <v>-16.83</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>1</v>

--- a/output/laminas_provinciales/prov_i_peringrmin_a_2023_aysen.xlsx
+++ b/output/laminas_provinciales/prov_i_peringrmin_a_2023_aysen.xlsx
@@ -55,7 +55,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 21:42</t>
+    <t xml:space="preserve">2026-10-05 07:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
